--- a/docs/rapp-workshop/downloads/FY27 RAPP Workshop BOM and Readiness.xlsx
+++ b/docs/rapp-workshop/downloads/FY27 RAPP Workshop BOM and Readiness.xlsx
@@ -15,11 +15,13 @@
     <sheet name="Customer Touchpoints" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Risk Register" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Package Manifest" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Public Links" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'BOM &amp; Ownership'!$A$1:$I$29</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Customer Touchpoints'!$A$1:$I$12</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Package Manifest'!$A$1:$I$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Package Manifest'!$A$1:$I$17</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Public Links'!$A$1:$I$19</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Readiness Dashboard'!$A$1:$I$11</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Rehearsal Plan'!$A$1:$I$8</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Risk Register'!$A$1:$I$14</definedName>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="551">
   <si>
     <t xml:space="preserve">FY27 RAPP Workshop BOM and Readiness</t>
   </si>
@@ -79,7 +81,7 @@
     <t xml:space="preserve">Main deck</t>
   </si>
   <si>
-    <t xml:space="preserve">FY27 RAPP Workshop Deck.pptx with speaker notes</t>
+    <t xml:space="preserve">FY27 RAPP Workshop Deck.pptx paired with the facilitator guide</t>
   </si>
   <si>
     <t xml:space="preserve">Lead facilitator</t>
@@ -88,7 +90,7 @@
     <t xml:space="preserve">T-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Deck opens; notes visible; all links work</t>
+    <t xml:space="preserve">Deck opens without repair; guide talk track and links work</t>
   </si>
   <si>
     <t xml:space="preserve">Workshop package</t>
@@ -577,7 +579,7 @@
     <t xml:space="preserve">Facilitator Rehearsal Plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Complete all three passes; record actual timing and evidence.</t>
+    <t xml:space="preserve">Complete all four passes; record actual timing and evidence.</t>
   </si>
   <si>
     <t xml:space="preserve">Pass</t>
@@ -1306,7 +1308,7 @@
     <t xml:space="preserve">Live</t>
   </si>
   <si>
-    <t xml:space="preserve">Renders cleanly; notes present</t>
+    <t xml:space="preserve">Renders cleanly; facilitator guide included</t>
   </si>
   <si>
     <t xml:space="preserve">Package root</t>
@@ -1385,6 +1387,309 @@
   </si>
   <si>
     <t xml:space="preserve">Not shared before build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bom.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portable online BOM and readiness view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planning/review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local XLSX and tentative public URLs are cross-referenced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending merge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">facilitator-guide.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browser-readable delivery runbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepare/rehearse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content matches DOCX guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customer-communications.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browser-readable pre/post templates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content matches DOCX pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">examples.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browser-readable synthetic inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop/rehearsal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No PII; transcript and FAQ included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scoring-guide.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browser-readable answer key and rubric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content matches DOCX scorecard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tentative Public Links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These GitHub Pages URLs become live after the public workshop PR merges to microsoft/aibast-agents-library main.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tentative published URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source branch URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop landing page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/index.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After PR merge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public entry point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessible HTML overview and download index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOM - online HTML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/bom.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/bom.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portable BOM/readiness review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">References the local XLSX download and tentative published URLs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facilitator guide - HTML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/facilitator-guide.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/facilitator-guide.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portable browser runbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same source content as DOCX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer communications - HTML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/customer-communications.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/customer-communications.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portable pre/post templates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example inputs - HTML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/examples.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/examples.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portable synthetic inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No PII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoring guide - HTML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/scoring-guide.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/scoring-guide.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portable rehearsal answer key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/FY27%20RAPP%20Workshop%20Deck.pptx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/FY27%20RAPP%20Workshop%20Deck.pptx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerPoint-compatible; talk track is in facilitator guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/FY27%20RAPP%20Facilitator%20Guide.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/FY27%20RAPP%20Facilitator%20Guide.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery runbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepare, rehearse, deliver, recover, follow up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/FY27%20RAPP%20Customer%20Communications%20Pack.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/FY27%20RAPP%20Customer%20Communications%20Pack.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace template tokens before sending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOM and readiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/FY27%20RAPP%20Workshop%20BOM%20and%20Readiness.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/FY27%20RAPP%20Workshop%20BOM%20and%20Readiness.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Readiness and ownership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/Example%20Inputs/01%20Facilities%20Discovery%20Transcript.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/Example%20Inputs/01%20Facilities%20Discovery%20Transcript.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synthetic narrative input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance FAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/Example%20Inputs/02%20Facilities%20Maintenance%20FAQ.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/Example%20Inputs/02%20Facilities%20Maintenance%20FAQ.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synthetic knowledge input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/Example%20Inputs/03%20Sample%20Service%20Requests.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/Example%20Inputs/03%20Sample%20Service%20Requests.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synthetic structured input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected MVP and scoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/Facilitator%20Rehearsal/Expected%20MVP%20and%20Scoring%20Guide.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/Facilitator%20Rehearsal/Expected%20MVP%20and%20Scoring%20Guide.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehearsal answer key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facilitator-facing but publicly safe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR compare link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/microsoft/aibast-agents-library/compare/main...kody-w:aibast-agents-library:docs/fy27-rapp-workshop?expand=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open or complete the PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repository maintainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated PR submission was blocked by account SAML/EMU policy</t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1700,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1423,6 +1728,13 @@
       <color rgb="FF1B1A19"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1488,7 +1800,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1512,56 +1824,61 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -1733,6 +2050,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BOMTable" displayName="BOMTable" ref="A4:I29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A4:I29"/>
@@ -1751,8 +2072,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ManifestTable" displayName="ManifestTable" ref="A4:I12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A4:I12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ManifestTable" displayName="ManifestTable" ref="A4:I17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:I17"/>
   <tableColumns count="9">
     <tableColumn id="1" name="File"/>
     <tableColumn id="2" name="Audience"/>
@@ -1768,7 +2089,24 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RehearsalTable" displayName="RehearsalTable" ref="A4:I8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PublicLinksTable" displayName="PublicLinksTable" ref="A4:I19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:I19"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Asset"/>
+    <tableColumn id="2" name="Tentative published URL"/>
+    <tableColumn id="3" name="Source branch URL"/>
+    <tableColumn id="4" name="Availability"/>
+    <tableColumn id="5" name="Use"/>
+    <tableColumn id="6" name="Review owner"/>
+    <tableColumn id="7" name="Last verified"/>
+    <tableColumn id="8" name="Status"/>
+    <tableColumn id="9" name="Notes"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RehearsalTable" displayName="RehearsalTable" ref="A4:I8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A4:I8"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Pass"/>
@@ -1784,8 +2122,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RiskTable" displayName="RiskTable" ref="A4:I14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="RiskTable" displayName="RiskTable" ref="A4:I14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A4:I14"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
@@ -1801,8 +2139,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="RunOfShowTable" displayName="RunOfShowTable" ref="A4:I17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RunOfShowTable" displayName="RunOfShowTable" ref="A4:I17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A4:I17"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Time"/>
@@ -1818,8 +2156,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TouchpointTable" displayName="TouchpointTable" ref="A4:I12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TouchpointTable" displayName="TouchpointTable" ref="A4:I12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A4:I12"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Timing"/>
@@ -2018,805 +2356,805 @@
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2862,196 +3200,190 @@
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="3" t="n">
         <f aca="false">COUNTA('BOM &amp; Ownership'!A5:A200)</f>
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="3" t="n">
         <f aca="false">COUNTIF('BOM &amp; Ownership'!I5:I200,"Complete")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="3" t="n">
         <f aca="false">COUNTIF('BOM &amp; Ownership'!I5:I200,"In progress")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="3" t="n">
         <f aca="false">COUNTIF('BOM &amp; Ownership'!I5:I200,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="3" t="n">
         <f aca="false">COUNTIF('BOM &amp; Ownership'!I5:I200,"Not started")</f>
         <v>25</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="4" t="n">
         <f aca="false">IF(B5=0,0,B6/B5)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B11" s="6" t="str">
-        <f aca="false">IF(B8&gt;0,"NO-GO: BLOCKERS",IF(B9&gt;0,"AT RISK","GO"))</f>
+      <c r="B11" s="5" t="str">
+        <f aca="false">IF(B8&gt;0,"NO-GO: BLOCKERS",IF(B6=B5,"GO","AT RISK"))</f>
         <v>AT RISK</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I11"/>
@@ -3078,188 +3410,188 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3297,431 +3629,431 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4" t="s">
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4" t="s">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4" t="s">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4" t="s">
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4" t="s">
+      <c r="H14" s="3"/>
+      <c r="I14" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4" t="s">
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4" t="s">
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4" t="s">
+      <c r="H17" s="3"/>
+      <c r="I17" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3759,295 +4091,295 @@
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4" t="s">
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4" t="s">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4" t="s">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4085,368 +4417,368 @@
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>363</v>
       </c>
     </row>
@@ -4481,320 +4813,465 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>426</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:I17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -4811,4 +5288,578 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="42"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I19"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H19" type="list">
+      <formula1>"Pending merge,Branch published,Live,Deprecated"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/"/>
+    <hyperlink ref="C5" r:id="rId2" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/index.html"/>
+    <hyperlink ref="B6" r:id="rId3" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/bom.html"/>
+    <hyperlink ref="C6" r:id="rId4" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/bom.html"/>
+    <hyperlink ref="B7" r:id="rId5" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/facilitator-guide.html"/>
+    <hyperlink ref="C7" r:id="rId6" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/facilitator-guide.html"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/customer-communications.html"/>
+    <hyperlink ref="C8" r:id="rId8" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/customer-communications.html"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/examples.html"/>
+    <hyperlink ref="C9" r:id="rId10" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/examples.html"/>
+    <hyperlink ref="B10" r:id="rId11" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/scoring-guide.html"/>
+    <hyperlink ref="C10" r:id="rId12" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/scoring-guide.html"/>
+    <hyperlink ref="B11" r:id="rId13" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/FY27%20RAPP%20Workshop%20Deck.pptx"/>
+    <hyperlink ref="C11" r:id="rId14" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/FY27%20RAPP%20Workshop%20Deck.pptx"/>
+    <hyperlink ref="B12" r:id="rId15" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/FY27%20RAPP%20Facilitator%20Guide.docx"/>
+    <hyperlink ref="C12" r:id="rId16" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/FY27%20RAPP%20Facilitator%20Guide.docx"/>
+    <hyperlink ref="B13" r:id="rId17" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/FY27%20RAPP%20Customer%20Communications%20Pack.docx"/>
+    <hyperlink ref="C13" r:id="rId18" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/FY27%20RAPP%20Customer%20Communications%20Pack.docx"/>
+    <hyperlink ref="B14" r:id="rId19" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/FY27%20RAPP%20Workshop%20BOM%20and%20Readiness.xlsx"/>
+    <hyperlink ref="C14" r:id="rId20" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/FY27%20RAPP%20Workshop%20BOM%20and%20Readiness.xlsx"/>
+    <hyperlink ref="B15" r:id="rId21" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/Example%20Inputs/01%20Facilities%20Discovery%20Transcript.docx"/>
+    <hyperlink ref="C15" r:id="rId22" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/Example%20Inputs/01%20Facilities%20Discovery%20Transcript.docx"/>
+    <hyperlink ref="B16" r:id="rId23" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/Example%20Inputs/02%20Facilities%20Maintenance%20FAQ.docx"/>
+    <hyperlink ref="C16" r:id="rId24" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/Example%20Inputs/02%20Facilities%20Maintenance%20FAQ.docx"/>
+    <hyperlink ref="B17" r:id="rId25" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/Example%20Inputs/03%20Sample%20Service%20Requests.xlsx"/>
+    <hyperlink ref="C17" r:id="rId26" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/Example%20Inputs/03%20Sample%20Service%20Requests.xlsx"/>
+    <hyperlink ref="B18" r:id="rId27" display="https://microsoft.github.io/aibast-agents-library/docs/rapp-workshop/downloads/Facilitator%20Rehearsal/Expected%20MVP%20and%20Scoring%20Guide.docx"/>
+    <hyperlink ref="C18" r:id="rId28" display="https://github.com/kody-w/aibast-agents-library/blob/docs/fy27-rapp-workshop/docs/rapp-workshop/downloads/Facilitator%20Rehearsal/Expected%20MVP%20and%20Scoring%20Guide.docx"/>
+    <hyperlink ref="C19" r:id="rId29" display="https://github.com/microsoft/aibast-agents-library/compare/main...kody-w:aibast-agents-library:docs/fy27-rapp-workshop?expand=1"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId30"/>
+  <tableParts>
+    <tablePart r:id="rId31"/>
+  </tableParts>
+</worksheet>
 </file>